--- a/data/barcode/master_data.xlsx
+++ b/data/barcode/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjhda\OneDrive\바탕 화면\barcode_server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3622A92D-EBA5-4FF8-AA10-E6B9AFA77357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB60ABC2-E664-4342-B767-469B8D7624AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="1635" windowWidth="19260" windowHeight="13815" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO매핑" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7378" uniqueCount="4692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7374" uniqueCount="4692">
   <si>
     <t>바코드</t>
   </si>
@@ -15174,8 +15174,8 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>154</v>
+      <c r="A80" s="4">
+        <v>8807649240178</v>
       </c>
       <c r="B80" t="s">
         <v>155</v>
@@ -36711,8 +36711,8 @@
       <c r="A538" t="s">
         <v>155</v>
       </c>
-      <c r="B538" t="s">
-        <v>154</v>
+      <c r="B538" s="4">
+        <v>8807649240178</v>
       </c>
     </row>
     <row r="539" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
@@ -44614,7 +44614,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2EE4D5-B15B-42EA-9F52-2EDBF117079F}">
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
@@ -45041,553 +45041,545 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>159</v>
+        <v>3552</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>3552</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s">
-        <v>3553</v>
+        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="B75" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>322</v>
+        <v>860</v>
       </c>
       <c r="B76" t="s">
-        <v>323</v>
+        <v>861</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="B77" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>866</v>
+        <v>2020</v>
       </c>
       <c r="B78" t="s">
-        <v>867</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>2020</v>
+        <v>2860</v>
       </c>
       <c r="B79" t="s">
-        <v>2021</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>2860</v>
+        <v>1760</v>
       </c>
       <c r="B80" t="s">
-        <v>2861</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="B81" t="s">
-        <v>1761</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="B82" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="B83" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1772</v>
+        <v>1785</v>
       </c>
       <c r="B84" t="s">
-        <v>1773</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="B85" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="B86" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="B87" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="B88" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1797</v>
+        <v>1763</v>
       </c>
       <c r="B89" t="s">
-        <v>1798</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1763</v>
+        <v>2342</v>
       </c>
       <c r="B90" t="s">
-        <v>1764</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>2342</v>
+        <v>2347</v>
       </c>
       <c r="B91" t="s">
-        <v>2343</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>2347</v>
+        <v>2994</v>
       </c>
       <c r="B92" t="s">
-        <v>2348</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>2994</v>
+        <v>2617</v>
       </c>
       <c r="B93" t="s">
-        <v>2995</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>2617</v>
+        <v>2723</v>
       </c>
       <c r="B94" t="s">
-        <v>2618</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>2723</v>
+        <v>2870</v>
       </c>
       <c r="B95" t="s">
-        <v>2724</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>2870</v>
+        <v>2799</v>
       </c>
       <c r="B96" t="s">
-        <v>2871</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>2799</v>
+        <v>3143</v>
       </c>
       <c r="B97" t="s">
-        <v>2800</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>3143</v>
+        <v>3224</v>
       </c>
       <c r="B98" t="s">
-        <v>3144</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>3224</v>
+        <v>3227</v>
       </c>
       <c r="B99" t="s">
-        <v>3225</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>3227</v>
+        <v>3248</v>
       </c>
       <c r="B100" t="s">
-        <v>3228</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>3248</v>
+        <v>2937</v>
       </c>
       <c r="B101" t="s">
-        <v>3249</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>2937</v>
+        <v>2940</v>
       </c>
       <c r="B102" t="s">
-        <v>2938</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>2940</v>
+        <v>2750</v>
       </c>
       <c r="B103" t="s">
-        <v>2941</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>2750</v>
+        <v>2753</v>
       </c>
       <c r="B104" t="s">
-        <v>2751</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>2753</v>
+        <v>2756</v>
       </c>
       <c r="B105" t="s">
-        <v>2754</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>2756</v>
+        <v>2759</v>
       </c>
       <c r="B106" t="s">
-        <v>2757</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>2759</v>
+        <v>2762</v>
       </c>
       <c r="B107" t="s">
-        <v>2760</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="B108" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>2765</v>
+        <v>2570</v>
       </c>
       <c r="B109" t="s">
-        <v>2766</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>2570</v>
+        <v>3199</v>
       </c>
       <c r="B110" t="s">
-        <v>2571</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>3199</v>
+        <v>3251</v>
       </c>
       <c r="B111" t="s">
-        <v>3200</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>3251</v>
+        <v>1354</v>
       </c>
       <c r="B112" t="s">
-        <v>3252</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="B113" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="B114" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="B115" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B116" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="B117" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="B118" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="B119" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="B120" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="B121" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="B122" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B123" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B124" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="B125" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B126" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="B127" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="B128" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B129" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1405</v>
+        <v>1442</v>
       </c>
       <c r="B130" t="s">
-        <v>1406</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="B131" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="B132" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="B133" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="B134" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="B135" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1457</v>
+        <v>2328</v>
       </c>
       <c r="B136" t="s">
-        <v>1458</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="B137" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>2331</v>
+        <v>2863</v>
       </c>
       <c r="B138" t="s">
-        <v>2332</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>2863</v>
+        <v>2776</v>
       </c>
       <c r="B139" t="s">
-        <v>2864</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>2776</v>
-      </c>
-      <c r="B140" t="s">
         <v>2777</v>
       </c>
     </row>

--- a/data/barcode/master_data.xlsx
+++ b/data/barcode/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjhda\OneDrive\바탕 화면\barcode_server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA553A4E-DCB4-401B-9A9F-840AB914AF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB04EDE4-EDAE-497B-A96F-0AB72344FEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO매핑" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7318" uniqueCount="4677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7320" uniqueCount="4678">
   <si>
     <t>바코드</t>
   </si>
@@ -14114,6 +14114,10 @@
   </si>
   <si>
     <t>USB-PCI243</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NNO-콘넥터098</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -14124,7 +14128,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14151,6 +14155,12 @@
       <color indexed="8"/>
       <name val="NanumGothic"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="나눔고딕"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -14188,7 +14198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -14204,6 +14214,9 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14510,7 +14523,7 @@
   <dimension ref="A1:B2321"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" customWidth="1"/>
   </cols>
@@ -33003,8 +33016,13 @@
         <v>4654</v>
       </c>
     </row>
-    <row r="2312" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2312" s="4"/>
+    <row r="2312" spans="1:2" ht="30" x14ac:dyDescent="0.3">
+      <c r="A2312" s="6" t="s">
+        <v>4412</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>4677</v>
+      </c>
     </row>
     <row r="2313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2313" s="4"/>

--- a/data/barcode/master_data.xlsx
+++ b/data/barcode/master_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjhda\OneDrive\바탕 화면\barcode_server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB04EDE4-EDAE-497B-A96F-0AB72344FEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B5A1ECA-29C7-43B0-A948-2B8A2529BC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7320" uniqueCount="4678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7319" uniqueCount="4678">
   <si>
     <t>바코드</t>
   </si>
@@ -13904,10 +13904,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAB-U6F023</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CAB-U7F006</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -14118,6 +14114,10 @@
   </si>
   <si>
     <t>NNO-콘넥터098</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NEO-자재용011</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -15005,7 +15005,7 @@
         <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>4645</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -15509,7 +15509,7 @@
         <v>237</v>
       </c>
       <c r="B123" t="s">
-        <v>4663</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
@@ -20693,7 +20693,7 @@
         <v>1487</v>
       </c>
       <c r="B771" t="s">
-        <v>4673</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.3">
@@ -20709,7 +20709,7 @@
         <v>1490</v>
       </c>
       <c r="B773" t="s">
-        <v>4674</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
@@ -23109,7 +23109,7 @@
         <v>2077</v>
       </c>
       <c r="B1073" t="s">
-        <v>4664</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="1074" spans="1:2" x14ac:dyDescent="0.3">
@@ -23693,7 +23693,7 @@
         <v>2220</v>
       </c>
       <c r="B1146" t="s">
-        <v>4675</v>
+        <v>4674</v>
       </c>
     </row>
     <row r="1147" spans="1:2" x14ac:dyDescent="0.3">
@@ -25061,7 +25061,7 @@
         <v>2554</v>
       </c>
       <c r="B1317" t="s">
-        <v>2555</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="1318" spans="1:2" x14ac:dyDescent="0.3">
@@ -25397,7 +25397,7 @@
         <v>2634</v>
       </c>
       <c r="B1359" t="s">
-        <v>4672</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="1360" spans="1:2" x14ac:dyDescent="0.3">
@@ -26237,7 +26237,7 @@
         <v>2823</v>
       </c>
       <c r="B1464" t="s">
-        <v>4662</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="1465" spans="1:2" x14ac:dyDescent="0.3">
@@ -31989,7 +31989,7 @@
         <v>4188</v>
       </c>
       <c r="B2183" t="s">
-        <v>4661</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="2184" spans="1:2" x14ac:dyDescent="0.3">
@@ -32005,7 +32005,7 @@
         <v>4191</v>
       </c>
       <c r="B2185" t="s">
-        <v>4659</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="2186" spans="1:2" x14ac:dyDescent="0.3">
@@ -32013,7 +32013,7 @@
         <v>4192</v>
       </c>
       <c r="B2186" t="s">
-        <v>4660</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="2187" spans="1:2" x14ac:dyDescent="0.3">
@@ -32397,7 +32397,7 @@
         <v>4286</v>
       </c>
       <c r="B2234" t="s">
-        <v>4669</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="2235" spans="1:2" x14ac:dyDescent="0.3">
@@ -32405,7 +32405,7 @@
         <v>4287</v>
       </c>
       <c r="B2235" t="s">
-        <v>4668</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="2236" spans="1:2" x14ac:dyDescent="0.3">
@@ -32413,7 +32413,7 @@
         <v>4288</v>
       </c>
       <c r="B2236" t="s">
-        <v>4667</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="2237" spans="1:2" x14ac:dyDescent="0.3">
@@ -32421,7 +32421,7 @@
         <v>4289</v>
       </c>
       <c r="B2237" t="s">
-        <v>4666</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="2238" spans="1:2" x14ac:dyDescent="0.3">
@@ -32429,7 +32429,7 @@
         <v>4290</v>
       </c>
       <c r="B2238" t="s">
-        <v>4665</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="2239" spans="1:2" x14ac:dyDescent="0.3">
@@ -32525,7 +32525,7 @@
         <v>4313</v>
       </c>
       <c r="B2250" t="s">
-        <v>4670</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="2251" spans="1:2" x14ac:dyDescent="0.3">
@@ -32541,7 +32541,7 @@
         <v>4316</v>
       </c>
       <c r="B2252" t="s">
-        <v>4676</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="2253" spans="1:2" x14ac:dyDescent="0.3">
@@ -32629,7 +32629,7 @@
         <v>4337</v>
       </c>
       <c r="B2263" t="s">
-        <v>4646</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="2264" spans="1:2" x14ac:dyDescent="0.3">
@@ -32933,7 +32933,7 @@
         <v>8817649850208</v>
       </c>
       <c r="B2301" t="s">
-        <v>4647</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="2302" spans="1:2" x14ac:dyDescent="0.3">
@@ -32941,7 +32941,7 @@
         <v>8817649850215</v>
       </c>
       <c r="B2302" t="s">
-        <v>4648</v>
+        <v>4647</v>
       </c>
     </row>
     <row r="2303" spans="1:2" x14ac:dyDescent="0.3">
@@ -32949,7 +32949,7 @@
         <v>8817649850222</v>
       </c>
       <c r="B2303" t="s">
-        <v>4649</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="2304" spans="1:2" x14ac:dyDescent="0.3">
@@ -32957,7 +32957,7 @@
         <v>8817649850239</v>
       </c>
       <c r="B2304" t="s">
-        <v>4671</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="2305" spans="1:2" x14ac:dyDescent="0.3">
@@ -32965,7 +32965,7 @@
         <v>8817649850147</v>
       </c>
       <c r="B2305" t="s">
-        <v>4650</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="2306" spans="1:2" x14ac:dyDescent="0.3">
@@ -32973,7 +32973,7 @@
         <v>8817649850154</v>
       </c>
       <c r="B2306" t="s">
-        <v>4651</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="2307" spans="1:2" x14ac:dyDescent="0.3">
@@ -32981,7 +32981,7 @@
         <v>8817649850178</v>
       </c>
       <c r="B2307" t="s">
-        <v>4652</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="2308" spans="1:2" x14ac:dyDescent="0.3">
@@ -32989,7 +32989,7 @@
         <v>8817649850062</v>
       </c>
       <c r="B2308" t="s">
-        <v>4653</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="2309" spans="1:2" x14ac:dyDescent="0.3">
@@ -32997,7 +32997,7 @@
         <v>8817649850079</v>
       </c>
       <c r="B2309" t="s">
-        <v>4655</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="2310" spans="1:2" x14ac:dyDescent="0.3">
@@ -33005,7 +33005,7 @@
         <v>8817649850093</v>
       </c>
       <c r="B2310" t="s">
-        <v>4656</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="2311" spans="1:2" x14ac:dyDescent="0.3">
@@ -33013,15 +33013,15 @@
         <v>8817649850109</v>
       </c>
       <c r="B2311" t="s">
-        <v>4654</v>
-      </c>
-    </row>
-    <row r="2312" spans="1:2" ht="30" x14ac:dyDescent="0.3">
+        <v>4653</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2312" s="6" t="s">
         <v>4412</v>
       </c>
       <c r="B2312" t="s">
-        <v>4677</v>
+        <v>4676</v>
       </c>
     </row>
     <row r="2313" spans="1:2" x14ac:dyDescent="0.3">
@@ -43283,7 +43283,7 @@
     </row>
     <row r="1670" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1670" t="s">
-        <v>4647</v>
+        <v>4646</v>
       </c>
       <c r="B1670" s="4">
         <v>8817649850208</v>
@@ -43291,7 +43291,7 @@
     </row>
     <row r="1671" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1671" t="s">
-        <v>4648</v>
+        <v>4647</v>
       </c>
       <c r="B1671" s="4">
         <v>8817649850215</v>
@@ -43299,7 +43299,7 @@
     </row>
     <row r="1672" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1672" t="s">
-        <v>4649</v>
+        <v>4648</v>
       </c>
       <c r="B1672" s="4">
         <v>8817649850222</v>
@@ -43307,7 +43307,7 @@
     </row>
     <row r="1673" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1673" t="s">
-        <v>4646</v>
+        <v>4645</v>
       </c>
       <c r="B1673" s="4">
         <v>8817649850239</v>
@@ -43315,7 +43315,7 @@
     </row>
     <row r="1674" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1674" t="s">
-        <v>4650</v>
+        <v>4649</v>
       </c>
       <c r="B1674" s="4">
         <v>8817649850147</v>
@@ -43323,7 +43323,7 @@
     </row>
     <row r="1675" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1675" t="s">
-        <v>4651</v>
+        <v>4650</v>
       </c>
       <c r="B1675" s="4">
         <v>8817649850154</v>
@@ -43331,7 +43331,7 @@
     </row>
     <row r="1676" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1676" t="s">
-        <v>4652</v>
+        <v>4651</v>
       </c>
       <c r="B1676" s="4">
         <v>8817649850178</v>
@@ -43339,7 +43339,7 @@
     </row>
     <row r="1677" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1677" t="s">
-        <v>4653</v>
+        <v>4652</v>
       </c>
       <c r="B1677" s="4">
         <v>8817649850062</v>
@@ -43347,7 +43347,7 @@
     </row>
     <row r="1678" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1678" t="s">
-        <v>4655</v>
+        <v>4654</v>
       </c>
       <c r="B1678" s="4">
         <v>8817649850079</v>
@@ -43355,7 +43355,7 @@
     </row>
     <row r="1679" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1679" t="s">
-        <v>4656</v>
+        <v>4655</v>
       </c>
       <c r="B1679" s="4">
         <v>8817649850093</v>
@@ -43363,7 +43363,7 @@
     </row>
     <row r="1680" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1680" t="s">
-        <v>4654</v>
+        <v>4653</v>
       </c>
       <c r="B1680" s="4">
         <v>8817649850109</v>
@@ -43787,16 +43787,13 @@
       <c r="A39" s="2" t="s">
         <v>1924</v>
       </c>
-      <c r="B39" t="s">
-        <v>4623</v>
-      </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B40" t="s">
-        <v>4624</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -43804,7 +43801,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>4625</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -43812,7 +43809,7 @@
         <v>1536</v>
       </c>
       <c r="B42" t="s">
-        <v>4626</v>
+        <v>4625</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -43820,7 +43817,7 @@
         <v>4599</v>
       </c>
       <c r="B43" t="s">
-        <v>4627</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -43828,7 +43825,7 @@
         <v>3285</v>
       </c>
       <c r="B44" t="s">
-        <v>4628</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -43836,7 +43833,7 @@
         <v>2841</v>
       </c>
       <c r="B45" t="s">
-        <v>4629</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -43844,7 +43841,7 @@
         <v>3144</v>
       </c>
       <c r="B46" t="s">
-        <v>4627</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -43852,7 +43849,7 @@
         <v>3186</v>
       </c>
       <c r="B47" t="s">
-        <v>4630</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -43860,7 +43857,7 @@
         <v>2588</v>
       </c>
       <c r="B48" t="s">
-        <v>4631</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -43868,7 +43865,7 @@
         <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>4632</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -43892,7 +43889,7 @@
         <v>4344</v>
       </c>
       <c r="B52" t="s">
-        <v>4633</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -43900,7 +43897,7 @@
         <v>253</v>
       </c>
       <c r="B53" t="s">
-        <v>4634</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -43908,7 +43905,7 @@
         <v>265</v>
       </c>
       <c r="B54" t="s">
-        <v>4635</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -43916,7 +43913,7 @@
         <v>2743</v>
       </c>
       <c r="B55" t="s">
-        <v>4636</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -43924,7 +43921,7 @@
         <v>2737</v>
       </c>
       <c r="B56" t="s">
-        <v>4637</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -43932,7 +43929,7 @@
         <v>2857</v>
       </c>
       <c r="B57" t="s">
-        <v>4638</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -43940,7 +43937,7 @@
         <v>2863</v>
       </c>
       <c r="B58" t="s">
-        <v>4639</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -43948,7 +43945,7 @@
         <v>2860</v>
       </c>
       <c r="B59" t="s">
-        <v>4640</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -43956,7 +43953,7 @@
         <v>4600</v>
       </c>
       <c r="B60" t="s">
-        <v>4641</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -43964,7 +43961,7 @@
         <v>4601</v>
       </c>
       <c r="B61" t="s">
-        <v>4642</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -43972,7 +43969,7 @@
         <v>3427</v>
       </c>
       <c r="B62" t="s">
-        <v>4643</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -44262,7 +44259,7 @@
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>4644</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
@@ -44520,12 +44517,12 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>4657</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>4658</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
